--- a/dev_test/Diversification/Self Created Dataset/Manual Created Diversified Dataset/Disturbed Diversifications/HR_Timesheets/HR_Timesheets_original_0.xlsx
+++ b/dev_test/Diversification/Self Created Dataset/Manual Created Diversified Dataset/Disturbed Diversifications/HR_Timesheets/HR_Timesheets_original_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\table-diversification\dev_test\Diversification\Self Created Dataset\Manual Created Diversified Dataset\Disturbed Diversifications\HR_Timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21E060B-EE16-4DF7-8C85-AF72367196B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D99551-2E88-4C41-B638-880A95AFE359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timesheets" sheetId="1" r:id="rId1"/>
@@ -620,9 +620,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,7 +657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -692,7 +692,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -727,7 +727,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -762,7 +762,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>25</v>
       </c>
@@ -797,7 +797,7 @@
         <v>412.5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -832,7 +832,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -867,42 +867,42 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>8</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>65</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>16</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>520</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -937,7 +937,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -972,7 +972,7 @@
         <v>487.5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>73</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>76</v>
       </c>
